--- a/resources/templates/standard/K1100-02.xlsx
+++ b/resources/templates/standard/K1100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">    PURCHASE ORDER (원소재 생산 의뢰서)</t>
   </si>
@@ -1050,7 +1053,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1075,7 +1080,7 @@
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1198,7 +1203,7 @@
     <row r="7" ht="20.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="7"/>
@@ -1224,7 +1229,7 @@
     <row r="8" ht="20.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="7"/>
@@ -1250,7 +1255,7 @@
     <row r="9" ht="20.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="7"/>
@@ -1258,11 +1263,11 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -1280,7 +1285,7 @@
     <row r="10" ht="20.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="7"/>
@@ -1288,11 +1293,11 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -1310,7 +1315,7 @@
     <row r="11" ht="20.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="7"/>
@@ -1318,11 +1323,11 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -1340,7 +1345,7 @@
     <row r="12" ht="20.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="7"/>
@@ -1348,11 +1353,11 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -1370,7 +1375,7 @@
     <row r="13" ht="21" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="7"/>
@@ -1378,11 +1383,11 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1447,52 +1452,52 @@
     </row>
     <row r="16" ht="21" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O16" s="13"/>
       <c r="P16" s="14"/>
       <c r="Q16" s="15"/>
       <c r="R16" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V16" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" ht="41.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1500,38 +1505,38 @@
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
       <c r="P17" s="14"/>
       <c r="Q17" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R17" s="22">
         <v>43132</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
@@ -1556,7 +1561,7 @@
       <c r="N18" s="25"/>
       <c r="O18" s="25"/>
       <c r="P18" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q18" s="31"/>
       <c r="R18" s="32"/>
@@ -1584,7 +1589,7 @@
       <c r="N19" s="37"/>
       <c r="O19" s="37"/>
       <c r="P19" s="43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q19" s="43"/>
       <c r="R19" s="32"/>
@@ -1612,7 +1617,7 @@
       <c r="N20" s="37"/>
       <c r="O20" s="37"/>
       <c r="P20" s="43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q20" s="43"/>
       <c r="R20" s="32"/>
@@ -1640,7 +1645,7 @@
       <c r="N21" s="37"/>
       <c r="O21" s="37"/>
       <c r="P21" s="43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q21" s="43"/>
       <c r="R21" s="32"/>
@@ -1668,7 +1673,7 @@
       <c r="N22" s="37"/>
       <c r="O22" s="37"/>
       <c r="P22" s="31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q22" s="31"/>
       <c r="R22" s="32"/>
@@ -1679,7 +1684,7 @@
     </row>
     <row r="23" ht="24.95" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="44"/>
       <c r="C23" s="44"/>
@@ -1754,7 +1759,7 @@
     <row r="26" ht="14.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="55"/>
       <c r="B26" s="56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" s="57"/>
       <c r="D26" s="57"/>
@@ -1780,7 +1785,7 @@
     <row r="27" ht="21.75" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="55"/>
       <c r="B27" s="60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -1806,7 +1811,7 @@
     <row r="28" ht="14.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="55"/>
       <c r="B28" s="60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="60"/>
       <c r="D28" s="60"/>
@@ -1832,7 +1837,7 @@
     <row r="29" ht="23.25" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="55"/>
       <c r="B29" s="60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" s="60"/>
       <c r="D29" s="60"/>
@@ -1882,7 +1887,7 @@
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" s="62"/>
       <c r="D31" s="62"/>
@@ -1890,7 +1895,7 @@
       <c r="F31" s="62"/>
       <c r="G31" s="63"/>
       <c r="H31" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31" s="62"/>
       <c r="J31" s="62"/>
@@ -1910,7 +1915,7 @@
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="61"/>
       <c r="B32" s="60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="62"/>
       <c r="D32" s="62"/>
@@ -1936,7 +1941,7 @@
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" s="62"/>
       <c r="D33" s="62"/>
@@ -1962,7 +1967,7 @@
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="61"/>
       <c r="B34" s="60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C34" s="62"/>
       <c r="D34" s="62"/>
@@ -1988,7 +1993,7 @@
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="60" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" s="62"/>
       <c r="D35" s="62"/>
@@ -2014,7 +2019,7 @@
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="61"/>
       <c r="B36" s="60" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" s="62"/>
       <c r="D36" s="62"/>
@@ -2040,7 +2045,7 @@
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37" s="62"/>
       <c r="D37" s="62"/>
